--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/147.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/147.xlsx
@@ -426,13 +426,13 @@
         <v>-2.846194868759176</v>
       </c>
       <c r="E2">
-        <v>-15.30926471479653</v>
+        <v>-14.3665813375678</v>
       </c>
       <c r="F2">
-        <v>0.4946519920275918</v>
+        <v>0.5260073549583587</v>
       </c>
       <c r="G2">
-        <v>-7.17825042237897</v>
+        <v>-7.071213864003254</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.185130987705392</v>
       </c>
       <c r="E3">
-        <v>-14.63329939967157</v>
+        <v>-15.48102973390746</v>
       </c>
       <c r="F3">
-        <v>0.6022751417341092</v>
+        <v>0.3518638177048327</v>
       </c>
       <c r="G3">
-        <v>-6.65642237120581</v>
+        <v>-6.848288348479811</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.644187209205003</v>
       </c>
       <c r="E4">
-        <v>-14.76218882687789</v>
+        <v>-15.61969160802233</v>
       </c>
       <c r="F4">
-        <v>0.1202282692274097</v>
+        <v>0.6068841779632856</v>
       </c>
       <c r="G4">
-        <v>-7.416864613213019</v>
+        <v>-6.878960552901159</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.163428628867752</v>
       </c>
       <c r="E5">
-        <v>-16.7980820573503</v>
+        <v>-15.85638588745524</v>
       </c>
       <c r="F5">
-        <v>0.02779240748381846</v>
+        <v>0.7048336531399104</v>
       </c>
       <c r="G5">
-        <v>-6.91587975675511</v>
+        <v>-6.803271550236802</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.712741463455092</v>
       </c>
       <c r="E6">
-        <v>-15.70219587596807</v>
+        <v>-16.81223806709827</v>
       </c>
       <c r="F6">
-        <v>-0.2203052863894391</v>
+        <v>0.8342097308439428</v>
       </c>
       <c r="G6">
-        <v>-6.588291344007609</v>
+        <v>-7.019963308509797</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.250596376058403</v>
       </c>
       <c r="E7">
-        <v>-15.49414419463368</v>
+        <v>-16.29063031699877</v>
       </c>
       <c r="F7">
-        <v>0.256979301918566</v>
+        <v>0.9006928418578255</v>
       </c>
       <c r="G7">
-        <v>-5.773347590787378</v>
+        <v>-6.432103116010333</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.74115229175571</v>
       </c>
       <c r="E8">
-        <v>-18.21523629873268</v>
+        <v>-17.75392518004531</v>
       </c>
       <c r="F8">
-        <v>0.5869785092740135</v>
+        <v>0.6992131803119157</v>
       </c>
       <c r="G8">
-        <v>-6.047278681434372</v>
+        <v>-5.987000268255323</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.139791290698316</v>
       </c>
       <c r="E9">
-        <v>-18.41140979274496</v>
+        <v>-19.17969257899028</v>
       </c>
       <c r="F9">
-        <v>0.1347131016327618</v>
+        <v>0.8399884218458721</v>
       </c>
       <c r="G9">
-        <v>-4.691001142723596</v>
+        <v>-5.620450045056138</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.412300766841241</v>
       </c>
       <c r="E10">
-        <v>-18.17232900751</v>
+        <v>-19.34975489187433</v>
       </c>
       <c r="F10">
-        <v>0.1169553896189488</v>
+        <v>0.6324144613175664</v>
       </c>
       <c r="G10">
-        <v>-4.608462621338486</v>
+        <v>-5.526347788102354</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.529791356149311</v>
       </c>
       <c r="E11">
-        <v>-18.4411301676573</v>
+        <v>-20.05543152496361</v>
       </c>
       <c r="F11">
-        <v>0.1806261933003273</v>
+        <v>1.210715969294763</v>
       </c>
       <c r="G11">
-        <v>-5.683486142669401</v>
+        <v>-5.615086961282519</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.470977491759446</v>
       </c>
       <c r="E12">
-        <v>-19.76768322956822</v>
+        <v>-21.04948138286134</v>
       </c>
       <c r="F12">
-        <v>0.6422968844329645</v>
+        <v>1.010734824380517</v>
       </c>
       <c r="G12">
-        <v>-4.957850976462089</v>
+        <v>-4.907047344616433</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.223039770767413</v>
       </c>
       <c r="E13">
-        <v>-20.48125299285287</v>
+        <v>-20.67506262343315</v>
       </c>
       <c r="F13">
-        <v>0.7061880338434876</v>
+        <v>1.224485092264096</v>
       </c>
       <c r="G13">
-        <v>-3.344622135175239</v>
+        <v>-4.501724012061304</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.786827385999666</v>
       </c>
       <c r="E14">
-        <v>-21.14091127307621</v>
+        <v>-22.15912959675287</v>
       </c>
       <c r="F14">
-        <v>0.2187691987296333</v>
+        <v>1.402050615258587</v>
       </c>
       <c r="G14">
-        <v>-3.850930348860296</v>
+        <v>-4.050953510343061</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.171251616978139</v>
       </c>
       <c r="E15">
-        <v>-22.58418575253483</v>
+        <v>-22.89385639060135</v>
       </c>
       <c r="F15">
-        <v>0.5757383919854271</v>
+        <v>1.261541279660929</v>
       </c>
       <c r="G15">
-        <v>-1.877447941989956</v>
+        <v>-2.581213644364843</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.395601728219976</v>
       </c>
       <c r="E16">
-        <v>-23.26227945044339</v>
+        <v>-23.55374109452507</v>
       </c>
       <c r="F16">
-        <v>1.404151354992087</v>
+        <v>1.962495835501037</v>
       </c>
       <c r="G16">
-        <v>-4.386394537109714</v>
+        <v>-2.73770975309727</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.486279095809305</v>
       </c>
       <c r="E17">
-        <v>-23.67730503629836</v>
+        <v>-23.74839302127078</v>
       </c>
       <c r="F17">
-        <v>0.6741939996451622</v>
+        <v>1.593391888161634</v>
       </c>
       <c r="G17">
-        <v>-1.420552931024061</v>
+        <v>-2.741129546639338</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.474887968123099</v>
       </c>
       <c r="E18">
-        <v>-25.24635788132004</v>
+        <v>-25.5673315905097</v>
       </c>
       <c r="F18">
-        <v>1.17482280973146</v>
+        <v>1.508621738363549</v>
       </c>
       <c r="G18">
-        <v>-1.874316165909806</v>
+        <v>-2.63078575326989</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.399687356850526</v>
       </c>
       <c r="E19">
-        <v>-26.40358224313615</v>
+        <v>-25.32380384379922</v>
       </c>
       <c r="F19">
-        <v>1.163762448169281</v>
+        <v>1.945824113152295</v>
       </c>
       <c r="G19">
-        <v>-2.090100834705041</v>
+        <v>-0.8027885806683611</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.2996016736759033</v>
       </c>
       <c r="E20">
-        <v>-26.34553173483182</v>
+        <v>-26.77393443290546</v>
       </c>
       <c r="F20">
-        <v>1.469080448758318</v>
+        <v>2.596645873774976</v>
       </c>
       <c r="G20">
-        <v>-0.5561396958105006</v>
+        <v>-0.6758192276006934</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.7837619139068861</v>
       </c>
       <c r="E21">
-        <v>-26.36350071969426</v>
+        <v>-27.18314092966057</v>
       </c>
       <c r="F21">
-        <v>1.893073676942022</v>
+        <v>2.634275291414547</v>
       </c>
       <c r="G21">
-        <v>-1.376999393909409</v>
+        <v>-1.649996910714329</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.811103783616899</v>
       </c>
       <c r="E22">
-        <v>-26.66574013191419</v>
+        <v>-27.957392244648</v>
       </c>
       <c r="F22">
-        <v>1.639222143088919</v>
+        <v>2.414095235750438</v>
       </c>
       <c r="G22">
-        <v>-0.2233007578377147</v>
+        <v>-1.528254909053171</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.748442878761556</v>
       </c>
       <c r="E23">
-        <v>-27.29218205529127</v>
+        <v>-28.56275864999338</v>
       </c>
       <c r="F23">
-        <v>1.831875549958</v>
+        <v>2.476805961611972</v>
       </c>
       <c r="G23">
-        <v>-0.703624499585032</v>
+        <v>-0.477904883626444</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.563257049904931</v>
       </c>
       <c r="E24">
-        <v>-28.93041639772812</v>
+        <v>-27.58044206824952</v>
       </c>
       <c r="F24">
-        <v>2.663405659501394</v>
+        <v>2.798003765312675</v>
       </c>
       <c r="G24">
-        <v>-0.5432749158448928</v>
+        <v>-1.063232508788365</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.231026703942811</v>
       </c>
       <c r="E25">
-        <v>-29.22458606926638</v>
+        <v>-29.3261416273624</v>
       </c>
       <c r="F25">
-        <v>1.89912407245207</v>
+        <v>3.097668986745007</v>
       </c>
       <c r="G25">
-        <v>-0.4829534655738325</v>
+        <v>-0.07602782897769672</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.735257117387251</v>
       </c>
       <c r="E26">
-        <v>-29.10323655128284</v>
+        <v>-29.12277691662594</v>
       </c>
       <c r="F26">
-        <v>1.810089487264373</v>
+        <v>3.25203359552189</v>
       </c>
       <c r="G26">
-        <v>0.1772024204122349</v>
+        <v>0.192755363355731</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.062457291706969</v>
       </c>
       <c r="E27">
-        <v>-28.80934764513305</v>
+        <v>-30.58272976585481</v>
       </c>
       <c r="F27">
-        <v>2.418642972791808</v>
+        <v>3.118954715527343</v>
       </c>
       <c r="G27">
-        <v>-0.1365379803444955</v>
+        <v>-0.2462494595159426</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.211049516640383</v>
       </c>
       <c r="E28">
-        <v>-30.37025829388893</v>
+        <v>-29.98316207147626</v>
       </c>
       <c r="F28">
-        <v>2.49722521809098</v>
+        <v>2.680496535755954</v>
       </c>
       <c r="G28">
-        <v>-0.7075408749579898</v>
+        <v>-0.5565799983672237</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.188053210120758</v>
       </c>
       <c r="E29">
-        <v>-26.95808935690138</v>
+        <v>-29.88940680985846</v>
       </c>
       <c r="F29">
-        <v>1.845830227225561</v>
+        <v>2.915118348720469</v>
       </c>
       <c r="G29">
-        <v>-0.1157014067203226</v>
+        <v>-0.5733048744316217</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.005596245415783</v>
       </c>
       <c r="E30">
-        <v>-29.07679932002606</v>
+        <v>-28.79862874715689</v>
       </c>
       <c r="F30">
-        <v>2.122219981374033</v>
+        <v>2.642883685464439</v>
       </c>
       <c r="G30">
-        <v>-0.8078835102532995</v>
+        <v>-0.4422999663515823</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.681834750069219</v>
       </c>
       <c r="E31">
-        <v>-28.12476917244551</v>
+        <v>-28.73667469425796</v>
       </c>
       <c r="F31">
-        <v>2.201360546302692</v>
+        <v>2.740200287945325</v>
       </c>
       <c r="G31">
-        <v>-0.7611220545110939</v>
+        <v>-0.02388673673417553</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>4.238716071380742</v>
       </c>
       <c r="E32">
-        <v>-29.96024799299745</v>
+        <v>-28.85563317796545</v>
       </c>
       <c r="F32">
-        <v>2.000696826648539</v>
+        <v>2.684166203350355</v>
       </c>
       <c r="G32">
-        <v>0.4650543550518647</v>
+        <v>-1.142268472992925</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.698638124567394</v>
       </c>
       <c r="E33">
-        <v>-28.16068449980034</v>
+        <v>-29.48637715164981</v>
       </c>
       <c r="F33">
-        <v>2.642583816464626</v>
+        <v>2.526044120034375</v>
       </c>
       <c r="G33">
-        <v>0.4740093807355932</v>
+        <v>-0.568229808119919</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.085693037354294</v>
       </c>
       <c r="E34">
-        <v>-28.49693275181788</v>
+        <v>-28.63975629354579</v>
       </c>
       <c r="F34">
-        <v>1.913426664028806</v>
+        <v>2.345035902113849</v>
       </c>
       <c r="G34">
-        <v>-1.508828627828727</v>
+        <v>-0.8561843696712661</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.424084397466392</v>
       </c>
       <c r="E35">
-        <v>-27.25039329714848</v>
+        <v>-26.69900630197454</v>
       </c>
       <c r="F35">
-        <v>2.997325529774292</v>
+        <v>3.076568812260898</v>
       </c>
       <c r="G35">
-        <v>-2.314526027357774</v>
+        <v>-1.090345876754996</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.735884281453764</v>
       </c>
       <c r="E36">
-        <v>-26.71904479945848</v>
+        <v>-28.20279025112366</v>
       </c>
       <c r="F36">
-        <v>2.467985505506963</v>
+        <v>3.008135724380825</v>
       </c>
       <c r="G36">
-        <v>-1.123861839794577</v>
+        <v>-2.093093567872542</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.044028062452145</v>
       </c>
       <c r="E37">
-        <v>-26.83236533302643</v>
+        <v>-27.48120961731944</v>
       </c>
       <c r="F37">
-        <v>2.859950736428827</v>
+        <v>3.046984498837316</v>
       </c>
       <c r="G37">
-        <v>-1.920789604190094</v>
+        <v>-0.9236897037625449</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.3675386009735259</v>
       </c>
       <c r="E38">
-        <v>-26.55313509723947</v>
+        <v>-26.92425712759007</v>
       </c>
       <c r="F38">
-        <v>2.30092368117997</v>
+        <v>3.102271396034961</v>
       </c>
       <c r="G38">
-        <v>-0.868072538702789</v>
+        <v>-1.737143711490104</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.2788943575617659</v>
       </c>
       <c r="E39">
-        <v>-25.3792912358152</v>
+        <v>-26.42888282741701</v>
       </c>
       <c r="F39">
-        <v>2.749082043238142</v>
+        <v>3.137122469405542</v>
       </c>
       <c r="G39">
-        <v>-1.744913561870773</v>
+        <v>-1.801725833870206</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.8801601198956855</v>
       </c>
       <c r="E40">
-        <v>-25.21320945158389</v>
+        <v>-25.90220318642891</v>
       </c>
       <c r="F40">
-        <v>2.886875990489422</v>
+        <v>2.909536809160406</v>
       </c>
       <c r="G40">
-        <v>-1.875527825577179</v>
+        <v>-2.314036066617962</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.427876430051617</v>
       </c>
       <c r="E41">
-        <v>-22.06888163825401</v>
+        <v>-24.50999630835478</v>
       </c>
       <c r="F41">
-        <v>2.608310943541199</v>
+        <v>3.111330421951977</v>
       </c>
       <c r="G41">
-        <v>-3.078431099999061</v>
+        <v>-2.645706382015385</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.915797902476471</v>
       </c>
       <c r="E42">
-        <v>-23.93824929404235</v>
+        <v>-23.69393359285453</v>
       </c>
       <c r="F42">
-        <v>2.48935738449919</v>
+        <v>3.004209262891556</v>
       </c>
       <c r="G42">
-        <v>-2.886634644181385</v>
+        <v>-2.266897208684279</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.341732996009091</v>
       </c>
       <c r="E43">
-        <v>-21.43840031606209</v>
+        <v>-23.35393123588463</v>
       </c>
       <c r="F43">
-        <v>2.291680757699533</v>
+        <v>3.373457346159046</v>
       </c>
       <c r="G43">
-        <v>-2.157976949896718</v>
+        <v>-2.717147954752857</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.707254796660492</v>
       </c>
       <c r="E44">
-        <v>-22.86440319565547</v>
+        <v>-22.34622350037977</v>
       </c>
       <c r="F44">
-        <v>3.321793727981247</v>
+        <v>3.312055440793936</v>
       </c>
       <c r="G44">
-        <v>-2.464851279205</v>
+        <v>-3.513655279864887</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.014586227173075</v>
       </c>
       <c r="E45">
-        <v>-21.66101104133115</v>
+        <v>-23.009364177115</v>
       </c>
       <c r="F45">
-        <v>3.074257667207088</v>
+        <v>3.42327867523302</v>
       </c>
       <c r="G45">
-        <v>-2.115883363364885</v>
+        <v>-2.242283302599798</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.270882782735182</v>
       </c>
       <c r="E46">
-        <v>-21.32243968214768</v>
+        <v>-21.65354811616651</v>
       </c>
       <c r="F46">
-        <v>3.426408247280797</v>
+        <v>3.288087458361335</v>
       </c>
       <c r="G46">
-        <v>-2.576641780975109</v>
+        <v>-1.88524427673494</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.484829742073937</v>
       </c>
       <c r="E47">
-        <v>-20.63692381534055</v>
+        <v>-21.7965346829587</v>
       </c>
       <c r="F47">
-        <v>2.609165818700888</v>
+        <v>3.718011797149084</v>
       </c>
       <c r="G47">
-        <v>-3.101820104234012</v>
+        <v>-3.172076501668425</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.66452314456834</v>
       </c>
       <c r="E48">
-        <v>-18.26075199098377</v>
+        <v>-21.53596628855735</v>
       </c>
       <c r="F48">
-        <v>3.491287639002859</v>
+        <v>3.12628908051173</v>
       </c>
       <c r="G48">
-        <v>-2.998017948850164</v>
+        <v>-2.919836105394735</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.819583050400328</v>
       </c>
       <c r="E49">
-        <v>-19.82036749617346</v>
+        <v>-19.88694512103423</v>
       </c>
       <c r="F49">
-        <v>2.645564282379898</v>
+        <v>3.058397744913088</v>
       </c>
       <c r="G49">
-        <v>-3.121742967289346</v>
+        <v>-2.809505554207445</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.962062747909265</v>
       </c>
       <c r="E50">
-        <v>-16.8001515699718</v>
+        <v>-19.88667794106778</v>
       </c>
       <c r="F50">
-        <v>3.621064646529847</v>
+        <v>3.4496373259901</v>
       </c>
       <c r="G50">
-        <v>-2.123573760652612</v>
+        <v>-3.289302919214018</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.100300831099594</v>
       </c>
       <c r="E51">
-        <v>-19.45674009030554</v>
+        <v>-19.68968479326011</v>
       </c>
       <c r="F51">
-        <v>3.076307048161613</v>
+        <v>3.540055284740472</v>
       </c>
       <c r="G51">
-        <v>-3.417901060687007</v>
+        <v>-2.92826475433772</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.237894468746189</v>
       </c>
       <c r="E52">
-        <v>-17.29438016622093</v>
+        <v>-18.72669573858099</v>
       </c>
       <c r="F52">
-        <v>3.601798477475536</v>
+        <v>3.536715307372384</v>
       </c>
       <c r="G52">
-        <v>-2.781571170947074</v>
+        <v>-2.94475458166883</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.383978770256665</v>
       </c>
       <c r="E53">
-        <v>-15.38131273625856</v>
+        <v>-16.65687065236911</v>
       </c>
       <c r="F53">
-        <v>3.470813710275267</v>
+        <v>3.466971742261083</v>
       </c>
       <c r="G53">
-        <v>-4.145317300394447</v>
+        <v>-2.573652358353148</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.542436540898787</v>
       </c>
       <c r="E54">
-        <v>-15.88455299578295</v>
+        <v>-17.64274208620898</v>
       </c>
       <c r="F54">
-        <v>2.928860963932913</v>
+        <v>3.484524847526404</v>
       </c>
       <c r="G54">
-        <v>-3.698704843873528</v>
+        <v>-3.062209426856632</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.709323967749815</v>
       </c>
       <c r="E55">
-        <v>-13.85358221655688</v>
+        <v>-17.14422502507459</v>
       </c>
       <c r="F55">
-        <v>3.193870606701725</v>
+        <v>3.835378204247329</v>
       </c>
       <c r="G55">
-        <v>-3.296490113579775</v>
+        <v>-3.845891698549525</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.889910724115775</v>
       </c>
       <c r="E56">
-        <v>-15.42557404120953</v>
+        <v>-16.89957874528421</v>
       </c>
       <c r="F56">
-        <v>3.646525347022292</v>
+        <v>3.340579443941934</v>
       </c>
       <c r="G56">
-        <v>-4.048212378636545</v>
+        <v>-4.275024474623092</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.084194725684313</v>
       </c>
       <c r="E57">
-        <v>-15.54162977307811</v>
+        <v>-15.28904960682629</v>
       </c>
       <c r="F57">
-        <v>3.278349171174024</v>
+        <v>3.442877847983256</v>
       </c>
       <c r="G57">
-        <v>-3.882956566407206</v>
+        <v>-4.068092204599868</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.282915760488111</v>
       </c>
       <c r="E58">
-        <v>-13.7635018115963</v>
+        <v>-16.48283686778033</v>
       </c>
       <c r="F58">
-        <v>3.205085044600825</v>
+        <v>3.274434306828394</v>
       </c>
       <c r="G58">
-        <v>-3.843994755955523</v>
+        <v>-4.61566636843194</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.482246728400115</v>
       </c>
       <c r="E59">
-        <v>-14.64445755962647</v>
+        <v>-14.08066707414552</v>
       </c>
       <c r="F59">
-        <v>3.599800455299984</v>
+        <v>3.276811721274428</v>
       </c>
       <c r="G59">
-        <v>-5.292451124661767</v>
+        <v>-5.057647371743418</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.678050490041501</v>
       </c>
       <c r="E60">
-        <v>-12.82729868067256</v>
+        <v>-14.57418017150144</v>
       </c>
       <c r="F60">
-        <v>3.345617574485761</v>
+        <v>3.596849810611212</v>
       </c>
       <c r="G60">
-        <v>-4.947373099830296</v>
+        <v>-4.656213930196934</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.858980246391192</v>
       </c>
       <c r="E61">
-        <v>-14.56933017583922</v>
+        <v>-14.38306045448171</v>
       </c>
       <c r="F61">
-        <v>2.795304944314354</v>
+        <v>3.919475719714341</v>
       </c>
       <c r="G61">
-        <v>-4.53054231098066</v>
+        <v>-5.036459880292083</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.013743083844765</v>
       </c>
       <c r="E62">
-        <v>-12.64122368369738</v>
+        <v>-13.64285873555796</v>
       </c>
       <c r="F62">
-        <v>2.945408431171236</v>
+        <v>3.398257009464058</v>
       </c>
       <c r="G62">
-        <v>-5.128297724097005</v>
+        <v>-4.862739003118827</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.137487013090102</v>
       </c>
       <c r="E63">
-        <v>-13.35225297306373</v>
+        <v>-13.39868341706437</v>
       </c>
       <c r="F63">
-        <v>3.247886788303475</v>
+        <v>3.418054990390966</v>
       </c>
       <c r="G63">
-        <v>-3.982514602409708</v>
+        <v>-5.505133812286705</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.219267306358985</v>
       </c>
       <c r="E64">
-        <v>-12.6650298715557</v>
+        <v>-12.47613363527375</v>
       </c>
       <c r="F64">
-        <v>3.692660441153808</v>
+        <v>3.190873573438396</v>
       </c>
       <c r="G64">
-        <v>-4.819367546008836</v>
+        <v>-5.060256081628364</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.24576944994286</v>
       </c>
       <c r="E65">
-        <v>-12.3692435347967</v>
+        <v>-13.62577280312702</v>
       </c>
       <c r="F65">
-        <v>3.831827821558931</v>
+        <v>3.553756481582776</v>
       </c>
       <c r="G65">
-        <v>-4.642309638931994</v>
+        <v>-5.249208778827807</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.214186303302016</v>
       </c>
       <c r="E66">
-        <v>-12.92682548241314</v>
+        <v>-14.27944444071221</v>
       </c>
       <c r="F66">
-        <v>2.946102603054781</v>
+        <v>3.041914890332184</v>
       </c>
       <c r="G66">
-        <v>-4.8225258064533</v>
+        <v>-5.165425492319931</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.118035870683892</v>
       </c>
       <c r="E67">
-        <v>-9.598569168787714</v>
+        <v>-12.48661705260151</v>
       </c>
       <c r="F67">
-        <v>2.878151625003138</v>
+        <v>2.807236748384278</v>
       </c>
       <c r="G67">
-        <v>-4.55352742865982</v>
+        <v>-5.40653914503613</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.949209007456626</v>
       </c>
       <c r="E68">
-        <v>-12.18903744013547</v>
+        <v>-12.60969191918197</v>
       </c>
       <c r="F68">
-        <v>3.286737219494772</v>
+        <v>2.943854413923584</v>
       </c>
       <c r="G68">
-        <v>-4.730628372828671</v>
+        <v>-5.062672779872032</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.708553964949684</v>
       </c>
       <c r="E69">
-        <v>-12.12072540972976</v>
+        <v>-12.79866061104805</v>
       </c>
       <c r="F69">
-        <v>2.883070470640962</v>
+        <v>2.964836960236495</v>
       </c>
       <c r="G69">
-        <v>-4.664208897674274</v>
+        <v>-5.426455387000386</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.396841881023446</v>
       </c>
       <c r="E70">
-        <v>-12.60830167766162</v>
+        <v>-12.07141485626024</v>
       </c>
       <c r="F70">
-        <v>2.94860261587643</v>
+        <v>2.656912915798252</v>
       </c>
       <c r="G70">
-        <v>-5.270118184453843</v>
+        <v>-6.191889931680817</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.014130611646467</v>
       </c>
       <c r="E71">
-        <v>-11.4510139172094</v>
+        <v>-12.29893897582762</v>
       </c>
       <c r="F71">
-        <v>2.671010072259094</v>
+        <v>2.659053417167086</v>
       </c>
       <c r="G71">
-        <v>-5.819476732331583</v>
+        <v>-5.49943305286808</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.565877515735297</v>
       </c>
       <c r="E72">
-        <v>-11.94063252691872</v>
+        <v>-12.88818854217969</v>
       </c>
       <c r="F72">
-        <v>2.963206733187786</v>
+        <v>2.407920585129971</v>
       </c>
       <c r="G72">
-        <v>-4.728618871686334</v>
+        <v>-5.753798819377982</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.062509124421114</v>
       </c>
       <c r="E73">
-        <v>-11.7437299485912</v>
+        <v>-13.79847974483155</v>
       </c>
       <c r="F73">
-        <v>2.423149291463037</v>
+        <v>2.455361186288298</v>
       </c>
       <c r="G73">
-        <v>-4.413011323245454</v>
+        <v>-5.421542537420107</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.513635002343583</v>
       </c>
       <c r="E74">
-        <v>-11.53133093220944</v>
+        <v>-13.98836318844718</v>
       </c>
       <c r="F74">
-        <v>2.272744278871536</v>
+        <v>2.032459746341484</v>
       </c>
       <c r="G74">
-        <v>-5.289090920939406</v>
+        <v>-5.35557660700459</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.929658859907043</v>
       </c>
       <c r="E75">
-        <v>-12.26225833636549</v>
+        <v>-13.0897509202611</v>
       </c>
       <c r="F75">
-        <v>2.310877343892009</v>
+        <v>2.256360828378968</v>
       </c>
       <c r="G75">
-        <v>-4.379266932563663</v>
+        <v>-5.204003279489059</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.327286744571546</v>
       </c>
       <c r="E76">
-        <v>-11.93835470449286</v>
+        <v>-12.40289915362171</v>
       </c>
       <c r="F76">
-        <v>2.492836527590948</v>
+        <v>2.727506385864825</v>
       </c>
       <c r="G76">
-        <v>-5.565415536011294</v>
+        <v>-5.207383346484654</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.718519690206368</v>
       </c>
       <c r="E77">
-        <v>-14.46281593870481</v>
+        <v>-14.60088458272467</v>
       </c>
       <c r="F77">
-        <v>1.507614443601745</v>
+        <v>2.02235366402733</v>
       </c>
       <c r="G77">
-        <v>-3.929218129772981</v>
+        <v>-4.977429542781339</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.113414804288741</v>
       </c>
       <c r="E78">
-        <v>-14.5131725696701</v>
+        <v>-13.77045301919808</v>
       </c>
       <c r="F78">
-        <v>1.652875294621861</v>
+        <v>2.020093877752493</v>
       </c>
       <c r="G78">
-        <v>-4.011359385693378</v>
+        <v>-4.597322635598839</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.5245323791270136</v>
       </c>
       <c r="E79">
-        <v>-14.79989742993976</v>
+        <v>-13.85484113233101</v>
       </c>
       <c r="F79">
-        <v>1.64848991759144</v>
+        <v>2.048293160878593</v>
       </c>
       <c r="G79">
-        <v>-4.009704112923743</v>
+        <v>-4.690269512159417</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.04118275175652706</v>
       </c>
       <c r="E80">
-        <v>-15.51451327072018</v>
+        <v>-15.06333687686197</v>
       </c>
       <c r="F80">
-        <v>1.60082068702994</v>
+        <v>2.034931594671437</v>
       </c>
       <c r="G80">
-        <v>-3.644041115929082</v>
+        <v>-4.445822140085172</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.5781277593568406</v>
       </c>
       <c r="E81">
-        <v>-15.52034594524206</v>
+        <v>-15.42861264726868</v>
       </c>
       <c r="F81">
-        <v>1.399870352254419</v>
+        <v>1.942260476585451</v>
       </c>
       <c r="G81">
-        <v>-3.803817975290928</v>
+        <v>-3.811104486022864</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.082857498257009</v>
       </c>
       <c r="E82">
-        <v>-17.37669423825835</v>
+        <v>-14.81758564941372</v>
       </c>
       <c r="F82">
-        <v>2.54635900222063</v>
+        <v>1.866542725765159</v>
       </c>
       <c r="G82">
-        <v>-3.73662714302588</v>
+        <v>-4.018609480424382</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.552496088153775</v>
       </c>
       <c r="E83">
-        <v>-16.21090200361973</v>
+        <v>-18.10859979280006</v>
       </c>
       <c r="F83">
-        <v>1.826613760215418</v>
+        <v>1.820048120180829</v>
       </c>
       <c r="G83">
-        <v>-3.095506893890622</v>
+        <v>-2.972453916195912</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.984327722871166</v>
       </c>
       <c r="E84">
-        <v>-17.38502663043246</v>
+        <v>-19.00687695390956</v>
       </c>
       <c r="F84">
-        <v>1.570088256386078</v>
+        <v>1.494284355355895</v>
       </c>
       <c r="G84">
-        <v>-2.968799073920557</v>
+        <v>-3.658845875580703</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.376536533933414</v>
       </c>
       <c r="E85">
-        <v>-19.083294952789</v>
+        <v>-19.19501240655823</v>
       </c>
       <c r="F85">
-        <v>1.703346063739629</v>
+        <v>1.104217742521247</v>
       </c>
       <c r="G85">
-        <v>-3.440816656909842</v>
+        <v>-2.748786838471672</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.726135392593217</v>
       </c>
       <c r="E86">
-        <v>-18.79934151861204</v>
+        <v>-19.69891835176175</v>
       </c>
       <c r="F86">
-        <v>0.9755540607836224</v>
+        <v>1.321510109419197</v>
       </c>
       <c r="G86">
-        <v>-3.969431326438508</v>
+        <v>-2.767104086940459</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.030031825499965</v>
       </c>
       <c r="E87">
-        <v>-22.48587711030232</v>
+        <v>-21.70487836904346</v>
       </c>
       <c r="F87">
-        <v>1.03847022176105</v>
+        <v>0.9269819097530706</v>
       </c>
       <c r="G87">
-        <v>-2.046348664858033</v>
+        <v>-2.829368827443072</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.284632523617162</v>
       </c>
       <c r="E88">
-        <v>-21.13902742788902</v>
+        <v>-22.93765126272953</v>
       </c>
       <c r="F88">
-        <v>1.023723625256414</v>
+        <v>1.057607165500525</v>
       </c>
       <c r="G88">
-        <v>-2.115234496439188</v>
+        <v>-2.703038409664483</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.485603745237565</v>
       </c>
       <c r="E89">
-        <v>-23.16169751425902</v>
+        <v>-24.25054644703333</v>
       </c>
       <c r="F89">
-        <v>0.5924854957678246</v>
+        <v>0.8933982385087731</v>
       </c>
       <c r="G89">
-        <v>-1.565180733998201</v>
+        <v>-3.428143888585512</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.628433860127725</v>
       </c>
       <c r="E90">
-        <v>-24.83811142105455</v>
+        <v>-25.21359890034855</v>
       </c>
       <c r="F90">
-        <v>0.6307850626362598</v>
+        <v>0.4723001543978528</v>
       </c>
       <c r="G90">
-        <v>-3.338868407027986</v>
+        <v>-2.39812061276991</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.707504685526883</v>
       </c>
       <c r="E91">
-        <v>-26.51632313203111</v>
+        <v>-26.53185579787742</v>
       </c>
       <c r="F91">
-        <v>0.5322234239489662</v>
+        <v>0.9443925358251106</v>
       </c>
       <c r="G91">
-        <v>-3.503568047606727</v>
+        <v>-3.198527760527202</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.719201007145553</v>
       </c>
       <c r="E92">
-        <v>-27.60828765492269</v>
+        <v>-28.28971430970089</v>
       </c>
       <c r="F92">
-        <v>-0.243545962242382</v>
+        <v>0.1138473551236451</v>
       </c>
       <c r="G92">
-        <v>-2.669913090998536</v>
+        <v>-3.222496110231525</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.659756502248294</v>
       </c>
       <c r="E93">
-        <v>-29.18672802656226</v>
+        <v>-28.95805820307094</v>
       </c>
       <c r="F93">
-        <v>-0.2672670911889486</v>
+        <v>-0.1080880110669956</v>
       </c>
       <c r="G93">
-        <v>-2.875842265723361</v>
+        <v>-2.894325041469112</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.52566861173812</v>
       </c>
       <c r="E94">
-        <v>-31.85823786875128</v>
+        <v>-32.09081123683721</v>
       </c>
       <c r="F94">
-        <v>-0.1589265753116069</v>
+        <v>0.1243618225673792</v>
       </c>
       <c r="G94">
-        <v>-2.514128749557051</v>
+        <v>-2.862576909747501</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.318558279068109</v>
       </c>
       <c r="E95">
-        <v>-32.89710150542891</v>
+        <v>-33.18350484404402</v>
       </c>
       <c r="F95">
-        <v>0.1316721648970849</v>
+        <v>-0.2704513354853099</v>
       </c>
       <c r="G95">
-        <v>-2.750624191245967</v>
+        <v>-3.64904997133</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.038315831182944</v>
       </c>
       <c r="E96">
-        <v>-35.35178574789367</v>
+        <v>-36.94501385140529</v>
       </c>
       <c r="F96">
-        <v>-0.7735022918573937</v>
+        <v>-0.5012775690101978</v>
       </c>
       <c r="G96">
-        <v>-2.564680779941722</v>
+        <v>-3.248735494175789</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.694917802396335</v>
       </c>
       <c r="E97">
-        <v>-38.21770977194299</v>
+        <v>-37.8562243342807</v>
       </c>
       <c r="F97">
-        <v>-1.036538763472737</v>
+        <v>-0.4517983556735805</v>
       </c>
       <c r="G97">
-        <v>-2.775966417349088</v>
+        <v>-3.05286044625373</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.287465907405865</v>
       </c>
       <c r="E98">
-        <v>-39.76519349526613</v>
+        <v>-39.55828298938167</v>
       </c>
       <c r="F98">
-        <v>-0.7333065920039505</v>
+        <v>-0.6185553407963433</v>
       </c>
       <c r="G98">
-        <v>-2.974427001337317</v>
+        <v>-3.561148366171271</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.845462815922153</v>
       </c>
       <c r="E99">
-        <v>-42.70743362752972</v>
+        <v>-40.91269522338778</v>
       </c>
       <c r="F99">
-        <v>-1.3352364517786</v>
+        <v>-0.6647103157455262</v>
       </c>
       <c r="G99">
-        <v>-2.293566963548648</v>
+        <v>-3.872640906506836</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.360061582833534</v>
       </c>
       <c r="E100">
-        <v>-43.45660851769967</v>
+        <v>-44.68357590770792</v>
       </c>
       <c r="F100">
-        <v>-1.267799889884095</v>
+        <v>-0.9656942980831154</v>
       </c>
       <c r="G100">
-        <v>-3.577684541139931</v>
+        <v>-4.617480547387461</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.8852323911494311</v>
       </c>
       <c r="E101">
-        <v>-46.90114019418304</v>
+        <v>-46.89025374266861</v>
       </c>
       <c r="F101">
-        <v>-1.075708944481515</v>
+        <v>-0.786094304747349</v>
       </c>
       <c r="G101">
-        <v>-4.132879580803405</v>
+        <v>-4.800037270605031</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.3799339348847776</v>
       </c>
       <c r="E102">
-        <v>-47.67814934984114</v>
+        <v>-47.94272091526528</v>
       </c>
       <c r="F102">
-        <v>-1.828223572574073</v>
+        <v>-1.512814400284133</v>
       </c>
       <c r="G102">
-        <v>-2.932873033728385</v>
+        <v>-4.525328201756309</v>
       </c>
     </row>
   </sheetData>
